--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:15</t>
+    <t xml:space="preserve">2026-09-09 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:59</t>
+    <t xml:space="preserve">2026-09-17 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2018.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:47</t>
+    <t xml:space="preserve">2026-10-05 18:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -506,7 +506,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>898577.12</v>
+        <v>898577.13</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>857521.62</v>
+        <v>857521.63</v>
       </c>
     </row>
     <row r="12">
